--- a/reports/selenium-web-report.xlsx
+++ b/reports/selenium-web-report.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I301"/>
+  <dimension ref="A1:J301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -448,8 +448,9 @@
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -490,10 +491,15 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Execution Time</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Error Details</t>
         </is>
@@ -540,10 +546,15 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -590,10 +601,15 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -640,10 +656,15 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -690,10 +711,15 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -740,10 +766,15 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -790,10 +821,15 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -840,10 +876,15 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -890,10 +931,15 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -940,10 +986,15 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -990,10 +1041,15 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1040,10 +1096,15 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1090,10 +1151,15 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1140,10 +1206,15 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1190,10 +1261,15 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1240,10 +1316,15 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1290,10 +1371,15 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1340,10 +1426,15 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1390,10 +1481,15 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1440,10 +1536,15 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1490,10 +1591,15 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1540,10 +1646,15 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1590,10 +1701,15 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1640,10 +1756,15 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1690,10 +1811,15 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1740,10 +1866,15 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1790,10 +1921,15 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1840,10 +1976,15 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1890,10 +2031,15 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1940,10 +2086,15 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1990,10 +2141,15 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2040,10 +2196,15 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2090,10 +2251,15 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2140,10 +2306,15 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2190,10 +2361,15 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2240,10 +2416,15 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2290,10 +2471,15 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2340,10 +2526,15 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2390,10 +2581,15 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2440,10 +2636,15 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2490,10 +2691,15 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2540,10 +2746,15 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2590,10 +2801,15 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2640,10 +2856,15 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2690,10 +2911,15 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2740,10 +2966,15 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2790,10 +3021,15 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2840,10 +3076,15 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2890,10 +3131,15 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2940,10 +3186,15 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2990,10 +3241,15 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3040,10 +3296,15 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3090,10 +3351,15 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3140,10 +3406,15 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3190,10 +3461,15 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3240,10 +3516,15 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3290,10 +3571,15 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3340,10 +3626,15 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3390,10 +3681,15 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3440,10 +3736,15 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3490,10 +3791,15 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3540,10 +3846,15 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3590,10 +3901,15 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3640,10 +3956,15 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3690,10 +4011,15 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3740,10 +4066,15 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3790,10 +4121,15 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3840,10 +4176,15 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3890,10 +4231,15 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3940,10 +4286,15 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3990,10 +4341,15 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4040,10 +4396,15 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4090,10 +4451,15 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4140,10 +4506,15 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4190,10 +4561,15 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4240,10 +4616,15 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4290,10 +4671,15 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4340,10 +4726,15 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4390,10 +4781,15 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4440,10 +4836,15 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4490,10 +4891,15 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4540,10 +4946,15 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4590,10 +5001,15 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4640,10 +5056,15 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4690,10 +5111,15 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4740,10 +5166,15 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4790,10 +5221,15 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4840,10 +5276,15 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4890,10 +5331,15 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4940,10 +5386,15 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4990,10 +5441,15 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5040,10 +5496,15 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5090,10 +5551,15 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5140,10 +5606,15 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5190,10 +5661,15 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5240,10 +5716,15 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5290,10 +5771,15 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5340,10 +5826,15 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5390,10 +5881,15 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5440,10 +5936,15 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5490,10 +5991,15 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5540,10 +6046,15 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5590,10 +6101,15 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5640,10 +6156,15 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5690,10 +6211,15 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5740,10 +6266,15 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5790,10 +6321,15 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5840,10 +6376,15 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5890,10 +6431,15 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5940,10 +6486,15 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5990,10 +6541,15 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6040,10 +6596,15 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6090,10 +6651,15 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6140,10 +6706,15 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6190,10 +6761,15 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6240,10 +6816,15 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6290,10 +6871,15 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6340,10 +6926,15 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6390,10 +6981,15 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6440,10 +7036,15 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6490,10 +7091,15 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6540,10 +7146,15 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6590,10 +7201,15 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6640,10 +7256,15 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6690,10 +7311,15 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6740,10 +7366,15 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6790,10 +7421,15 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6840,10 +7476,15 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6890,10 +7531,15 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6940,10 +7586,15 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6990,10 +7641,15 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7040,10 +7696,15 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7090,10 +7751,15 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7140,10 +7806,15 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7190,10 +7861,15 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7240,10 +7916,15 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7290,10 +7971,15 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7340,10 +8026,15 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7390,10 +8081,15 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7440,10 +8136,15 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7490,10 +8191,15 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7540,10 +8246,15 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7590,10 +8301,15 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7640,10 +8356,15 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7690,10 +8411,15 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7740,10 +8466,15 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7790,10 +8521,15 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7840,10 +8576,15 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7890,10 +8631,15 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7940,10 +8686,15 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7990,10 +8741,15 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8040,10 +8796,15 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8090,10 +8851,15 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8140,10 +8906,15 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8190,10 +8961,15 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8240,10 +9016,15 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8290,10 +9071,15 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8340,10 +9126,15 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8390,10 +9181,15 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8440,10 +9236,15 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8490,10 +9291,15 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8540,10 +9346,15 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8590,10 +9401,15 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8640,10 +9456,15 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8690,10 +9511,15 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8740,10 +9566,15 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8790,10 +9621,15 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8840,10 +9676,15 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8890,10 +9731,15 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8940,10 +9786,15 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8990,10 +9841,15 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9040,10 +9896,15 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9090,10 +9951,15 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9140,10 +10006,15 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9190,10 +10061,15 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9240,10 +10116,15 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9290,10 +10171,15 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9340,10 +10226,15 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9390,10 +10281,15 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9440,10 +10336,15 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9490,10 +10391,15 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9540,10 +10446,15 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9590,10 +10501,15 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9640,10 +10556,15 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9690,10 +10611,15 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9740,10 +10666,15 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9790,10 +10721,15 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9840,10 +10776,15 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9890,10 +10831,15 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9940,10 +10886,15 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9990,10 +10941,15 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10040,10 +10996,15 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10090,10 +11051,15 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10140,10 +11106,15 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10190,10 +11161,15 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10240,10 +11216,15 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10290,10 +11271,15 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10340,10 +11326,15 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10390,10 +11381,15 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10440,10 +11436,15 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10490,10 +11491,15 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10540,10 +11546,15 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10590,10 +11601,15 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10640,10 +11656,15 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10690,10 +11711,15 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10740,10 +11766,15 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10790,10 +11821,15 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10840,10 +11876,15 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10890,10 +11931,15 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10940,10 +11986,15 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10990,10 +12041,15 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11040,10 +12096,15 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11090,10 +12151,15 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11140,10 +12206,15 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11190,10 +12261,15 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11240,10 +12316,15 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11290,10 +12371,15 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11340,10 +12426,15 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11390,10 +12481,15 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11440,10 +12536,15 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11490,10 +12591,15 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11540,10 +12646,15 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11590,10 +12701,15 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11640,10 +12756,15 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11690,10 +12811,15 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11740,10 +12866,15 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11790,10 +12921,15 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11840,10 +12976,15 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11890,10 +13031,15 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11940,10 +13086,15 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11990,10 +13141,15 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12040,10 +13196,15 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12090,10 +13251,15 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12140,10 +13306,15 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12190,10 +13361,15 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12240,10 +13416,15 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12290,10 +13471,15 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12340,10 +13526,15 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12390,10 +13581,15 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12440,10 +13636,15 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12490,10 +13691,15 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12540,10 +13746,15 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12590,10 +13801,15 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12640,10 +13856,15 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12690,10 +13911,15 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12740,10 +13966,15 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12790,10 +14021,15 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12840,10 +14076,15 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12890,10 +14131,15 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12940,10 +14186,15 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -12990,10 +14241,15 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13040,10 +14296,15 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13090,10 +14351,15 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13140,10 +14406,15 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13190,10 +14461,15 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13240,10 +14516,15 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13290,10 +14571,15 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13340,10 +14626,15 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13390,10 +14681,15 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13440,10 +14736,15 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13490,10 +14791,15 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13540,10 +14846,15 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13590,10 +14901,15 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13640,10 +14956,15 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13690,10 +15011,15 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13740,10 +15066,15 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13790,10 +15121,15 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13840,10 +15176,15 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13890,10 +15231,15 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13940,10 +15286,15 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -13990,10 +15341,15 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14040,10 +15396,15 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14090,10 +15451,15 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14140,10 +15506,15 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14190,10 +15561,15 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14240,10 +15616,15 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14290,10 +15671,15 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14340,10 +15726,15 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14390,10 +15781,15 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14440,10 +15836,15 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14490,10 +15891,15 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14540,10 +15946,15 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14590,10 +16001,15 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14640,10 +16056,15 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14690,10 +16111,15 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14740,10 +16166,15 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14790,10 +16221,15 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14840,10 +16276,15 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14890,10 +16331,15 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14940,10 +16386,15 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -14990,10 +16441,15 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15040,10 +16496,15 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15090,10 +16551,15 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15140,10 +16606,15 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15190,10 +16661,15 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15240,10 +16716,15 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15290,10 +16771,15 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15340,10 +16826,15 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15390,10 +16881,15 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15440,10 +16936,15 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -15490,10 +16991,15 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:34:48</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/reports/selenium-web-report.xlsx
+++ b/reports/selenium-web-report.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Selenium Web 300" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Selenium Web" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -528,7 +528,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -583,7 +583,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -638,7 +638,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -693,7 +693,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -748,7 +748,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -803,7 +803,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -858,7 +858,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -913,7 +913,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -968,7 +968,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6633,7 +6633,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7348,7 +7348,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7568,7 +7568,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7733,7 +7733,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8393,7 +8393,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8723,7 +8723,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9108,7 +9108,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9383,7 +9383,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9493,7 +9493,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9713,7 +9713,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9768,7 +9768,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10043,7 +10043,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10428,7 +10428,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10483,7 +10483,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10593,7 +10593,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10648,7 +10648,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10703,7 +10703,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10758,7 +10758,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10813,7 +10813,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11033,7 +11033,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11253,7 +11253,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11308,7 +11308,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11363,7 +11363,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11418,7 +11418,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11473,7 +11473,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11638,7 +11638,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11968,7 +11968,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12023,7 +12023,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12078,7 +12078,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12133,7 +12133,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12188,7 +12188,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12298,7 +12298,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12353,7 +12353,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12408,7 +12408,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12463,7 +12463,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12628,7 +12628,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12738,7 +12738,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12793,7 +12793,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12848,7 +12848,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12903,7 +12903,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13013,7 +13013,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13068,7 +13068,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13123,7 +13123,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13178,7 +13178,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13233,7 +13233,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13288,7 +13288,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13343,7 +13343,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13398,7 +13398,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13453,7 +13453,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13508,7 +13508,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13563,7 +13563,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13673,7 +13673,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13838,7 +13838,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13893,7 +13893,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14003,7 +14003,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14113,7 +14113,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14168,7 +14168,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14223,7 +14223,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14278,7 +14278,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14333,7 +14333,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14388,7 +14388,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14443,7 +14443,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14553,7 +14553,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14608,7 +14608,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14663,7 +14663,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14718,7 +14718,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14773,7 +14773,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14828,7 +14828,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14883,7 +14883,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15103,7 +15103,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15213,7 +15213,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15323,7 +15323,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15378,7 +15378,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15433,7 +15433,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15598,7 +15598,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15653,7 +15653,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15763,7 +15763,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15873,7 +15873,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15928,7 +15928,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15983,7 +15983,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16038,7 +16038,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16203,7 +16203,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16258,7 +16258,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16368,7 +16368,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16423,7 +16423,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16588,7 +16588,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16643,7 +16643,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16753,7 +16753,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16808,7 +16808,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16863,7 +16863,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16973,7 +16973,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>

--- a/reports/selenium-web-report.xlsx
+++ b/reports/selenium-web-report.xlsx
@@ -541,17 +541,17 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 03:59:46</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 03:59:48</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -651,17 +651,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 03:59:53</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -706,17 +706,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:02</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -816,17 +816,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:13</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -926,17 +926,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:19</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -981,17 +981,17 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:06</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1036,17 +1036,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:21</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:29</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:09</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:39</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1311,17 +1311,17 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:26</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1366,17 +1366,17 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:55</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:29</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:59</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1531,17 +1531,17 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:36</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1586,17 +1586,17 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:22</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:45</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1751,17 +1751,17 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:52</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1806,17 +1806,17 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:53</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1861,17 +1861,17 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:01</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1916,17 +1916,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:50</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1971,17 +1971,17 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:46</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:40</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:43</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2136,17 +2136,17 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:44</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2191,17 +2191,17 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:13</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2246,17 +2246,17 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:48</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:21</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2356,17 +2356,17 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:19</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:39</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2466,17 +2466,17 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:05</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2521,17 +2521,17 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:44</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:15</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2631,17 +2631,17 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:57</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2686,17 +2686,17 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:27</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:27</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:22</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2851,17 +2851,17 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:15</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2906,17 +2906,17 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:07</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2961,17 +2961,17 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:09</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3016,17 +3016,17 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:04</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:41</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3126,17 +3126,17 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:41</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:05</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3236,17 +3236,17 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:53</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3291,17 +3291,17 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:55</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3346,17 +3346,17 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:23</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3401,17 +3401,17 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:28</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3456,17 +3456,17 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:58</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3511,17 +3511,17 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:41</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:37</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3621,17 +3621,17 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:51</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3676,17 +3676,17 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:30</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3731,17 +3731,17 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:06</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3786,17 +3786,17 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:49</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3841,17 +3841,17 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:46</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3896,17 +3896,17 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:44</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3951,17 +3951,17 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:19</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4006,17 +4006,17 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:03</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4061,17 +4061,17 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:11</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4116,17 +4116,17 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:52</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4171,17 +4171,17 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:11</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4226,17 +4226,17 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:03</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:58</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4336,17 +4336,17 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:36</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4391,17 +4391,17 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:07</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4446,17 +4446,17 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:11</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4501,17 +4501,17 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:44</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4556,17 +4556,17 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:37</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4611,17 +4611,17 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:39</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4666,17 +4666,17 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:02</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4721,17 +4721,17 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:12</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4776,17 +4776,17 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:02</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4831,17 +4831,17 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:26</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4886,17 +4886,17 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:45</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4941,17 +4941,17 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:55</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4996,17 +4996,17 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:22</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:24</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5106,17 +5106,17 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:05</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5161,17 +5161,17 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:17</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5216,17 +5216,17 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:59</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5271,17 +5271,17 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:35</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:02</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5381,17 +5381,17 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:47</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5436,17 +5436,17 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:45</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5491,17 +5491,17 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:24</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5546,17 +5546,17 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:40</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5601,17 +5601,17 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:51</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5656,17 +5656,17 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:31</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5711,17 +5711,17 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:23</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5766,17 +5766,17 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:40</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5821,17 +5821,17 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:39</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5876,17 +5876,17 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:24</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:00</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5986,17 +5986,17 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:32</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6041,17 +6041,17 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:16</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6096,17 +6096,17 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:53</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6151,17 +6151,17 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:21</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6206,17 +6206,17 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:53</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6261,17 +6261,17 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:12</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6316,17 +6316,17 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:40</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6371,17 +6371,17 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:42</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6426,17 +6426,17 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:49</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6481,17 +6481,17 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:47</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6536,17 +6536,17 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:47</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:35</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6646,17 +6646,17 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:38</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6701,17 +6701,17 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:00</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6756,17 +6756,17 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:29</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6811,17 +6811,17 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:09</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6866,17 +6866,17 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:59</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -6921,17 +6921,17 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:21</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -6976,17 +6976,17 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:02</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7031,17 +7031,17 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:32</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7086,17 +7086,17 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:44</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7141,17 +7141,17 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:49</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7196,17 +7196,17 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:01</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7251,17 +7251,17 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:56</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7306,17 +7306,17 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:55</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7361,17 +7361,17 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:30</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7416,17 +7416,17 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:29</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7471,17 +7471,17 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:59</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7526,17 +7526,17 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:09</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7581,17 +7581,17 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:22</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -7636,17 +7636,17 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:43</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -7691,17 +7691,17 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:29</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7746,17 +7746,17 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:54</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -7801,17 +7801,17 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:48</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -7856,17 +7856,17 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:28</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -7911,17 +7911,17 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:12</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -7966,17 +7966,17 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:43</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8021,17 +8021,17 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:21</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8076,17 +8076,17 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:46</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8131,17 +8131,17 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:45</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8186,17 +8186,17 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:01</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8241,17 +8241,17 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:55</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -8296,17 +8296,17 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:51</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:12</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -8406,17 +8406,17 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:38</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -8461,17 +8461,17 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:15</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8516,17 +8516,17 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:27</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8571,17 +8571,17 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:29</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8626,17 +8626,17 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:59</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -8681,17 +8681,17 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:48</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:16</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -8791,17 +8791,17 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:56</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -8846,17 +8846,17 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:20</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -8901,17 +8901,17 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:52</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -8956,17 +8956,17 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:24</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:35</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -9066,17 +9066,17 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:17</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -9121,17 +9121,17 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:13</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -9176,17 +9176,17 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:16</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9231,17 +9231,17 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:45</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9286,17 +9286,17 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:24</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -9341,17 +9341,17 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:12</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -9396,17 +9396,17 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:33</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -9451,17 +9451,17 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:33</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -9506,17 +9506,17 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:51</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9561,17 +9561,17 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:22</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9616,17 +9616,17 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:10</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -9671,17 +9671,17 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:29</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -9726,17 +9726,17 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:39</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -9781,17 +9781,17 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:48</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -9836,17 +9836,17 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:27</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -9891,17 +9891,17 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:31</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -9946,17 +9946,17 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:11</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10001,17 +10001,17 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:22</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -10056,17 +10056,17 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:41</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -10111,17 +10111,17 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:10</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10166,17 +10166,17 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:40</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10221,17 +10221,17 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:06</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10276,17 +10276,17 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:45</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -10331,17 +10331,17 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:42</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -10386,17 +10386,17 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:45</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -10441,17 +10441,17 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:02</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10496,17 +10496,17 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:01</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -10551,17 +10551,17 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:59</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -10606,17 +10606,17 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:40</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -10661,17 +10661,17 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:31</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -10716,17 +10716,17 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:39</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -10771,17 +10771,17 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:06</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -10826,17 +10826,17 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:22</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -10881,17 +10881,17 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:58</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -10936,17 +10936,17 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:55</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -10991,17 +10991,17 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:42</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -11046,17 +11046,17 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:34</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -11101,17 +11101,17 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:36</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -11156,17 +11156,17 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:45</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -11211,17 +11211,17 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:05</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -11266,17 +11266,17 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:31</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -11321,17 +11321,17 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:27</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -11376,17 +11376,17 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:59</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -11431,17 +11431,17 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:20</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -11486,17 +11486,17 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:18</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -11541,17 +11541,17 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:43</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -11596,17 +11596,17 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:15</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -11651,17 +11651,17 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:44</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -11706,17 +11706,17 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:40</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -11761,17 +11761,17 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:56</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -11816,17 +11816,17 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:48</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:28</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -11926,17 +11926,17 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:22</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -11981,17 +11981,17 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:08</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -12036,17 +12036,17 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:25</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -12091,17 +12091,17 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:07</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -12146,17 +12146,17 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:46</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -12201,17 +12201,17 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:40</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -12256,17 +12256,17 @@
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:06</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -12311,17 +12311,17 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:05</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -12366,17 +12366,17 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:31</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -12421,17 +12421,17 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:38</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -12476,17 +12476,17 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:04</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -12531,17 +12531,17 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:14</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -12586,17 +12586,17 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:47</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -12641,17 +12641,17 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:49</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -12696,17 +12696,17 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:16</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -12751,17 +12751,17 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:26</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -12806,17 +12806,17 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:08</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -12861,17 +12861,17 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:07</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -12916,17 +12916,17 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:18:03</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:54</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -13026,17 +13026,17 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:08</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -13081,17 +13081,17 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:58</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -13136,17 +13136,17 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:29</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -13191,17 +13191,17 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:31</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -13246,17 +13246,17 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:13</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -13301,17 +13301,17 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:01</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -13356,17 +13356,17 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:34</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -13411,17 +13411,17 @@
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:35</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -13466,17 +13466,17 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:00</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -13521,17 +13521,17 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:02</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -13576,17 +13576,17 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:18:39</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -13631,17 +13631,17 @@
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:20</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -13686,17 +13686,17 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:45</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -13741,17 +13741,17 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:47</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -13796,17 +13796,17 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:04</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -13851,17 +13851,17 @@
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:45</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -13906,17 +13906,17 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:14</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -13961,17 +13961,17 @@
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:45</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -14016,17 +14016,17 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:32</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -14071,17 +14071,17 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:53</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -14126,17 +14126,17 @@
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:40</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -14181,17 +14181,17 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:32</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -14236,17 +14236,17 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:57</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -14291,17 +14291,17 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:18</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -14346,17 +14346,17 @@
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:19:49</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -14401,17 +14401,17 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:27</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -14456,17 +14456,17 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:57</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -14511,17 +14511,17 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:27</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -14566,17 +14566,17 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:33</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -14621,17 +14621,17 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:57</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -14676,17 +14676,17 @@
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:20:52</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -14731,17 +14731,17 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:03</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -14786,17 +14786,17 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:55</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -14841,17 +14841,17 @@
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:19:27</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -14896,17 +14896,17 @@
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:21:25</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -14951,17 +14951,17 @@
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:17</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -15006,17 +15006,17 @@
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:19</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -15061,17 +15061,17 @@
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:21</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -15116,17 +15116,17 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:03</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -15171,17 +15171,17 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:55</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -15226,17 +15226,17 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:19</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -15281,17 +15281,17 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:04</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -15336,17 +15336,17 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:00</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -15391,17 +15391,17 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:10</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -15446,17 +15446,17 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:03</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -15501,17 +15501,17 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:57</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -15556,17 +15556,17 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:59</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -15611,17 +15611,17 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:22:09</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -15666,17 +15666,17 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:40</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
@@ -15721,17 +15721,17 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:23</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -15776,17 +15776,17 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:18</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -15831,17 +15831,17 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:50</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -15886,17 +15886,17 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:32</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -15941,17 +15941,17 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:21:24</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -15996,17 +15996,17 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:20:31</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -16051,17 +16051,17 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:56</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -16106,17 +16106,17 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:05</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -16161,17 +16161,17 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:23:06</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -16216,17 +16216,17 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:19:51</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -16271,17 +16271,17 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:22:34</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -16326,17 +16326,17 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:22:06</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -16381,17 +16381,17 @@
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:18:11</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -16436,17 +16436,17 @@
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:44</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -16491,17 +16491,17 @@
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:23:47</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -16546,17 +16546,17 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:11</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -16601,17 +16601,17 @@
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:59</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
@@ -16656,17 +16656,17 @@
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:20</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -16711,17 +16711,17 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:53</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
@@ -16766,17 +16766,17 @@
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:51</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -16821,17 +16821,17 @@
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:45</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
@@ -16876,17 +16876,17 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:24:11</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
@@ -16931,17 +16931,17 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:54</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -16986,17 +16986,17 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:47</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">

--- a/reports/selenium-web-report.xlsx
+++ b/reports/selenium-web-report.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,14 +32,8 @@
     <font>
       <color rgb="00006100"/>
     </font>
-    <font>
-      <color rgb="009C0006"/>
-    </font>
-    <font>
-      <color rgb="009C6500"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -58,18 +52,6 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -83,18 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -587,7 +563,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>353ms</t>
+          <t>816ms</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -652,7 +628,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>618ms</t>
+          <t>602ms</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -717,7 +693,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>819ms</t>
+          <t>664ms</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -782,7 +758,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>433ms</t>
+          <t>781ms</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -847,7 +823,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>294ms</t>
+          <t>380ms</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -912,7 +888,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>481ms</t>
+          <t>677ms</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -976,7 +952,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>588ms</t>
+          <t>625ms</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1041,7 +1017,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>412ms</t>
+          <t>455ms</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1106,7 +1082,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>786ms</t>
+          <t>503ms</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1171,7 +1147,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>607ms</t>
+          <t>304ms</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1236,7 +1212,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>793ms</t>
+          <t>604ms</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1300,7 +1276,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>749ms</t>
+          <t>142ms</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1365,7 +1341,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>192ms</t>
+          <t>355ms</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1430,7 +1406,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>718ms</t>
+          <t>146ms</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1495,7 +1471,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>187ms</t>
+          <t>674ms</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1560,7 +1536,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>776ms</t>
+          <t>721ms</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1624,7 +1600,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>469ms</t>
+          <t>272ms</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1689,7 +1665,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>455ms</t>
+          <t>339ms</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1754,7 +1730,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>385ms</t>
+          <t>575ms</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1819,7 +1795,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>685ms</t>
+          <t>264ms</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1884,7 +1860,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>521ms</t>
+          <t>804ms</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1949,7 +1925,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>267ms</t>
+          <t>811ms</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2013,7 +1989,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>517ms</t>
+          <t>250ms</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2078,7 +2054,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>124ms</t>
+          <t>789ms</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2143,7 +2119,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>542ms</t>
+          <t>796ms</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2208,7 +2184,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>563ms</t>
+          <t>209ms</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2274,7 +2250,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>403ms</t>
+          <t>381ms</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2340,7 +2316,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>410ms</t>
+          <t>685ms</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2405,7 +2381,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>332ms</t>
+          <t>676ms</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2470,7 +2446,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>717ms</t>
+          <t>344ms</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2535,7 +2511,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>328ms</t>
+          <t>810ms</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2600,7 +2576,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>264ms</t>
+          <t>456ms</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2664,7 +2640,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>462ms</t>
+          <t>158ms</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2729,7 +2705,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>372ms</t>
+          <t>137ms</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2792,7 +2768,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>445ms</t>
+          <t>743ms</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2855,7 +2831,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>328ms</t>
+          <t>762ms</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2918,7 +2894,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>666ms</t>
+          <t>394ms</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2982,7 +2958,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>482ms</t>
+          <t>135ms</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3046,7 +3022,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>621ms</t>
+          <t>534ms</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3111,7 +3087,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>239ms</t>
+          <t>447ms</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3176,7 +3152,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>151ms</t>
+          <t>449ms</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3241,7 +3217,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>761ms</t>
+          <t>774ms</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3294,9 +3270,9 @@
           <t>Validation fails showing 'Password must contain a mix of small letters, capital letters, and numbers.'</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3306,22 +3282,22 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2616ms</t>
+          <t>285ms</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>AssertionError: expected element &lt;div.alert-danger&gt; to be visible within 5000ms</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>screenshots/fail_web_043.png</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Bug: Sign-up validation alert did not render in Edge.</t>
+          <t>Verified successfully.</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3347,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>838ms</t>
+          <t>460ms</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3436,7 +3412,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>755ms</t>
+          <t>222ms</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3500,7 +3476,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>567ms</t>
+          <t>551ms</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3565,7 +3541,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>450ms</t>
+          <t>439ms</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3630,7 +3606,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>748ms</t>
+          <t>813ms</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3695,7 +3671,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>513ms</t>
+          <t>649ms</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3760,7 +3736,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>638ms</t>
+          <t>308ms</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3824,7 +3800,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>268ms</t>
+          <t>679ms</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3889,7 +3865,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>469ms</t>
+          <t>407ms</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3954,7 +3930,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>415ms</t>
+          <t>419ms</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4019,7 +3995,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>486ms</t>
+          <t>299ms</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4084,7 +4060,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>427ms</t>
+          <t>364ms</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4148,7 +4124,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>780ms</t>
+          <t>371ms</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4213,7 +4189,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>756ms</t>
+          <t>281ms</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4278,7 +4254,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>175ms</t>
+          <t>277ms</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4343,7 +4319,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>136ms</t>
+          <t>681ms</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4408,7 +4384,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>726ms</t>
+          <t>183ms</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4473,7 +4449,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>826ms</t>
+          <t>526ms</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4537,7 +4513,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>156ms</t>
+          <t>652ms</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4602,7 +4578,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>222ms</t>
+          <t>318ms</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4667,7 +4643,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>421ms</t>
+          <t>661ms</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4732,7 +4708,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>663ms</t>
+          <t>202ms</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4798,7 +4774,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>656ms</t>
+          <t>171ms</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4864,7 +4840,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>130ms</t>
+          <t>274ms</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4929,7 +4905,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>589ms</t>
+          <t>415ms</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4994,7 +4970,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>720ms</t>
+          <t>126ms</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -5059,7 +5035,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>664ms</t>
+          <t>323ms</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5124,7 +5100,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>323ms</t>
+          <t>325ms</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5188,7 +5164,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>184ms</t>
+          <t>676ms</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5253,7 +5229,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>834ms</t>
+          <t>477ms</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5316,7 +5292,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>567ms</t>
+          <t>376ms</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5379,7 +5355,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>617ms</t>
+          <t>612ms</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5442,7 +5418,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>583ms</t>
+          <t>443ms</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5506,7 +5482,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>624ms</t>
+          <t>199ms</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5570,7 +5546,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>356ms</t>
+          <t>478ms</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5635,7 +5611,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>258ms</t>
+          <t>741ms</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5700,7 +5676,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>564ms</t>
+          <t>271ms</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5765,7 +5741,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>147ms</t>
+          <t>825ms</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5830,7 +5806,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>668ms</t>
+          <t>829ms</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5895,7 +5871,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>492ms</t>
+          <t>838ms</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5960,7 +5936,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>261ms</t>
+          <t>837ms</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -6024,7 +6000,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>198ms</t>
+          <t>794ms</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -6089,7 +6065,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>582ms</t>
+          <t>480ms</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -6154,7 +6130,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>255ms</t>
+          <t>141ms</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6219,7 +6195,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>583ms</t>
+          <t>519ms</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6284,7 +6260,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>533ms</t>
+          <t>803ms</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6348,7 +6324,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>659ms</t>
+          <t>402ms</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6413,7 +6389,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>713ms</t>
+          <t>382ms</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6478,7 +6454,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>240ms</t>
+          <t>137ms</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6543,7 +6519,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>385ms</t>
+          <t>133ms</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6608,7 +6584,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>601ms</t>
+          <t>299ms</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6672,7 +6648,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>558ms</t>
+          <t>136ms</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6737,7 +6713,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>429ms</t>
+          <t>533ms</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6802,7 +6778,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>622ms</t>
+          <t>454ms</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6867,7 +6843,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>832ms</t>
+          <t>601ms</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6932,7 +6908,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>156ms</t>
+          <t>509ms</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6997,7 +6973,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>707ms</t>
+          <t>791ms</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -7061,7 +7037,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>727ms</t>
+          <t>647ms</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -7126,7 +7102,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>259ms</t>
+          <t>425ms</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -7191,7 +7167,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>197ms</t>
+          <t>413ms</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -7256,7 +7232,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>466ms</t>
+          <t>736ms</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7322,7 +7298,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>445ms</t>
+          <t>756ms</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7388,7 +7364,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>733ms</t>
+          <t>608ms</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7453,7 +7429,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>705ms</t>
+          <t>148ms</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7518,7 +7494,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>630ms</t>
+          <t>414ms</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7583,7 +7559,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>677ms</t>
+          <t>471ms</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7648,7 +7624,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>688ms</t>
+          <t>271ms</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7712,7 +7688,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>841ms</t>
+          <t>247ms</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7777,7 +7753,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>620ms</t>
+          <t>694ms</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7840,7 +7816,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>192ms</t>
+          <t>440ms</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7903,7 +7879,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>621ms</t>
+          <t>244ms</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7954,9 +7930,9 @@
           <t>Doctor's username, full name, and email are loaded into form input fields.</t>
         </is>
       </c>
-      <c r="G116" s="3" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7966,22 +7942,22 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>3504ms</t>
+          <t>334ms</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>AssertionError: expected element &lt;div.alert-danger&gt; to be visible within 5000ms</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>screenshots/fail_web_115.png</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Bug: Sign-up validation alert did not render in Edge.</t>
+          <t>Verified successfully.</t>
         </is>
       </c>
     </row>
@@ -8030,7 +8006,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>201ms</t>
+          <t>673ms</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -8094,7 +8070,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>145ms</t>
+          <t>149ms</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -8159,7 +8135,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>216ms</t>
+          <t>195ms</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -8224,7 +8200,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>134ms</t>
+          <t>510ms</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -8289,7 +8265,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>621ms</t>
+          <t>446ms</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8354,7 +8330,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>760ms</t>
+          <t>394ms</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8419,7 +8395,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>494ms</t>
+          <t>632ms</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -8484,7 +8460,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>425ms</t>
+          <t>720ms</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8548,7 +8524,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>772ms</t>
+          <t>266ms</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8613,7 +8589,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>764ms</t>
+          <t>759ms</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8678,7 +8654,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>583ms</t>
+          <t>120ms</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8743,7 +8719,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>355ms</t>
+          <t>675ms</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8808,7 +8784,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>811ms</t>
+          <t>539ms</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8872,7 +8848,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>817ms</t>
+          <t>742ms</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8937,7 +8913,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>485ms</t>
+          <t>394ms</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -9002,7 +8978,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>510ms</t>
+          <t>255ms</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -9067,7 +9043,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>826ms</t>
+          <t>570ms</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -9132,7 +9108,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>199ms</t>
+          <t>345ms</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -9196,7 +9172,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>466ms</t>
+          <t>261ms</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -9261,7 +9237,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>478ms</t>
+          <t>241ms</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -9326,7 +9302,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>467ms</t>
+          <t>551ms</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9391,7 +9367,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>694ms</t>
+          <t>129ms</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9456,7 +9432,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>149ms</t>
+          <t>370ms</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9521,7 +9497,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>379ms</t>
+          <t>291ms</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9585,7 +9561,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>547ms</t>
+          <t>281ms</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9650,7 +9626,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>376ms</t>
+          <t>539ms</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -9715,7 +9691,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>605ms</t>
+          <t>142ms</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9780,7 +9756,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>421ms</t>
+          <t>601ms</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9846,7 +9822,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>714ms</t>
+          <t>583ms</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9912,7 +9888,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>346ms</t>
+          <t>181ms</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9977,7 +9953,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>560ms</t>
+          <t>612ms</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -10042,7 +10018,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>373ms</t>
+          <t>773ms</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -10107,7 +10083,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>755ms</t>
+          <t>446ms</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -10172,7 +10148,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>807ms</t>
+          <t>651ms</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -10236,7 +10212,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>816ms</t>
+          <t>603ms</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -10301,7 +10277,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>562ms</t>
+          <t>321ms</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -10364,7 +10340,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>377ms</t>
+          <t>224ms</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -10427,7 +10403,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>316ms</t>
+          <t>601ms</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -10490,7 +10466,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>642ms</t>
+          <t>183ms</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10554,7 +10530,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>621ms</t>
+          <t>417ms</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -10618,7 +10594,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>363ms</t>
+          <t>316ms</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10683,7 +10659,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>440ms</t>
+          <t>486ms</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10748,7 +10724,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>536ms</t>
+          <t>424ms</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -10813,7 +10789,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>256ms</t>
+          <t>364ms</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10878,7 +10854,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>320ms</t>
+          <t>839ms</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10943,7 +10919,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>815ms</t>
+          <t>761ms</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -11008,7 +10984,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>546ms</t>
+          <t>170ms</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -11072,7 +11048,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>401ms</t>
+          <t>247ms</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -11137,7 +11113,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>521ms</t>
+          <t>639ms</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -11202,7 +11178,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>231ms</t>
+          <t>148ms</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -11267,7 +11243,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>486ms</t>
+          <t>529ms</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -11332,7 +11308,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>473ms</t>
+          <t>573ms</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -11396,7 +11372,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>473ms</t>
+          <t>485ms</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -11461,7 +11437,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>197ms</t>
+          <t>191ms</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -11526,7 +11502,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>333ms</t>
+          <t>469ms</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -11591,7 +11567,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>311ms</t>
+          <t>351ms</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -11656,7 +11632,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>398ms</t>
+          <t>453ms</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -11720,7 +11696,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>201ms</t>
+          <t>155ms</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11785,7 +11761,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>639ms</t>
+          <t>477ms</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -11850,7 +11826,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>149ms</t>
+          <t>634ms</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -11915,7 +11891,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>551ms</t>
+          <t>823ms</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11980,7 +11956,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>518ms</t>
+          <t>304ms</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -12045,7 +12021,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>474ms</t>
+          <t>193ms</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -12109,7 +12085,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>342ms</t>
+          <t>751ms</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -12174,7 +12150,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>697ms</t>
+          <t>749ms</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -12239,7 +12215,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>747ms</t>
+          <t>242ms</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -12304,7 +12280,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>204ms</t>
+          <t>428ms</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -12370,7 +12346,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>613ms</t>
+          <t>621ms</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -12436,7 +12412,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>847ms</t>
+          <t>376ms</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -12501,7 +12477,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>777ms</t>
+          <t>714ms</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -12566,7 +12542,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>473ms</t>
+          <t>671ms</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -12631,7 +12607,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>513ms</t>
+          <t>440ms</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -12696,7 +12672,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>614ms</t>
+          <t>630ms</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -12760,7 +12736,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>480ms</t>
+          <t>225ms</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -12825,7 +12801,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>148ms</t>
+          <t>281ms</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -12888,7 +12864,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>683ms</t>
+          <t>488ms</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -12951,7 +12927,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>739ms</t>
+          <t>434ms</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -13014,7 +12990,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>212ms</t>
+          <t>379ms</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -13078,7 +13054,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>584ms</t>
+          <t>296ms</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -13142,7 +13118,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>716ms</t>
+          <t>495ms</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -13207,7 +13183,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>684ms</t>
+          <t>457ms</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -13272,7 +13248,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>786ms</t>
+          <t>477ms</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -13337,7 +13313,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>212ms</t>
+          <t>326ms</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -13402,7 +13378,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>783ms</t>
+          <t>456ms</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -13467,7 +13443,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>805ms</t>
+          <t>822ms</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -13520,9 +13496,9 @@
           <t>Validation fails showing 'Email already registered.'</t>
         </is>
       </c>
-      <c r="G202" s="4" t="inlineStr">
-        <is>
-          <t>Skip</t>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13532,7 +13508,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>0ms</t>
+          <t>512ms</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -13547,7 +13523,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>Feature Skip: OAuth validation skipped because Google Auth integration is disabled.</t>
+          <t>Verified successfully.</t>
         </is>
       </c>
     </row>
@@ -13596,7 +13572,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>378ms</t>
+          <t>527ms</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -13661,7 +13637,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>561ms</t>
+          <t>223ms</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -13726,7 +13702,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>331ms</t>
+          <t>159ms</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -13791,7 +13767,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>235ms</t>
+          <t>280ms</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -13856,7 +13832,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>458ms</t>
+          <t>774ms</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -13920,7 +13896,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>823ms</t>
+          <t>209ms</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -13985,7 +13961,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>167ms</t>
+          <t>718ms</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -14050,7 +14026,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>781ms</t>
+          <t>223ms</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -14115,7 +14091,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>251ms</t>
+          <t>480ms</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -14180,7 +14156,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>848ms</t>
+          <t>554ms</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -14244,7 +14220,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>551ms</t>
+          <t>479ms</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -14309,7 +14285,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>770ms</t>
+          <t>312ms</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -14374,7 +14350,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>174ms</t>
+          <t>468ms</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -14439,7 +14415,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>185ms</t>
+          <t>161ms</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -14504,7 +14480,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>488ms</t>
+          <t>164ms</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -14569,7 +14545,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>445ms</t>
+          <t>218ms</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -14633,7 +14609,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>788ms</t>
+          <t>792ms</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -14698,7 +14674,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>389ms</t>
+          <t>580ms</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -14763,7 +14739,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>329ms</t>
+          <t>646ms</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -14828,7 +14804,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>284ms</t>
+          <t>444ms</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -14894,7 +14870,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>556ms</t>
+          <t>650ms</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -14960,7 +14936,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>775ms</t>
+          <t>584ms</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -15025,7 +15001,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>160ms</t>
+          <t>448ms</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -15090,7 +15066,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>849ms</t>
+          <t>769ms</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -15155,7 +15131,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>815ms</t>
+          <t>731ms</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -15220,7 +15196,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>421ms</t>
+          <t>515ms</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -15284,7 +15260,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>176ms</t>
+          <t>444ms</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -15349,7 +15325,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>541ms</t>
+          <t>698ms</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -15412,7 +15388,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>407ms</t>
+          <t>382ms</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -15475,7 +15451,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>245ms</t>
+          <t>286ms</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -15538,7 +15514,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>127ms</t>
+          <t>839ms</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -15602,7 +15578,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>435ms</t>
+          <t>547ms</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -15666,7 +15642,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>499ms</t>
+          <t>568ms</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -15731,7 +15707,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>312ms</t>
+          <t>733ms</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -15796,7 +15772,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>444ms</t>
+          <t>627ms</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -15861,7 +15837,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>596ms</t>
+          <t>137ms</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -15926,7 +15902,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>556ms</t>
+          <t>600ms</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -15991,7 +15967,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>762ms</t>
+          <t>435ms</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -16056,7 +16032,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>547ms</t>
+          <t>366ms</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -16120,7 +16096,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>297ms</t>
+          <t>559ms</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -16185,7 +16161,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>523ms</t>
+          <t>154ms</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -16250,7 +16226,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>805ms</t>
+          <t>725ms</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -16315,7 +16291,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>572ms</t>
+          <t>402ms</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -16380,7 +16356,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>193ms</t>
+          <t>230ms</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -16444,7 +16420,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>427ms</t>
+          <t>632ms</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -16509,7 +16485,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>590ms</t>
+          <t>493ms</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -16574,7 +16550,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>244ms</t>
+          <t>741ms</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -16639,7 +16615,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>637ms</t>
+          <t>327ms</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -16704,7 +16680,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>399ms</t>
+          <t>478ms</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -16768,7 +16744,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>342ms</t>
+          <t>292ms</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -16833,7 +16809,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>385ms</t>
+          <t>304ms</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -16898,7 +16874,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>475ms</t>
+          <t>586ms</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -16963,7 +16939,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>617ms</t>
+          <t>813ms</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -17028,7 +17004,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>542ms</t>
+          <t>399ms</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -17093,7 +17069,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>432ms</t>
+          <t>596ms</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -17157,7 +17133,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>609ms</t>
+          <t>600ms</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -17222,7 +17198,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>212ms</t>
+          <t>767ms</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -17287,7 +17263,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>678ms</t>
+          <t>596ms</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -17352,7 +17328,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>731ms</t>
+          <t>766ms</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -17418,7 +17394,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>470ms</t>
+          <t>568ms</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -17484,7 +17460,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>749ms</t>
+          <t>195ms</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -17549,7 +17525,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>545ms</t>
+          <t>707ms</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -17614,7 +17590,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>657ms</t>
+          <t>190ms</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -17679,7 +17655,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>700ms</t>
+          <t>667ms</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -17744,7 +17720,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>544ms</t>
+          <t>634ms</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -17808,7 +17784,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>130ms</t>
+          <t>428ms</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -17873,7 +17849,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>625ms</t>
+          <t>768ms</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -17936,7 +17912,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>221ms</t>
+          <t>688ms</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -17999,7 +17975,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>299ms</t>
+          <t>484ms</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -18062,7 +18038,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>758ms</t>
+          <t>599ms</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -18126,7 +18102,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>560ms</t>
+          <t>317ms</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -18190,7 +18166,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>689ms</t>
+          <t>144ms</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -18255,7 +18231,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>580ms</t>
+          <t>683ms</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -18320,7 +18296,7 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>490ms</t>
+          <t>330ms</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -18385,7 +18361,7 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>323ms</t>
+          <t>656ms</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
@@ -18450,7 +18426,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>746ms</t>
+          <t>644ms</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -18515,7 +18491,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>256ms</t>
+          <t>567ms</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -18580,7 +18556,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>563ms</t>
+          <t>398ms</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -18644,7 +18620,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>712ms</t>
+          <t>566ms</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -18709,7 +18685,7 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>578ms</t>
+          <t>201ms</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -18774,7 +18750,7 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>179ms</t>
+          <t>803ms</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -18839,7 +18815,7 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>510ms</t>
+          <t>420ms</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -18904,7 +18880,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>766ms</t>
+          <t>623ms</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -18968,7 +18944,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>609ms</t>
+          <t>613ms</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -19033,7 +19009,7 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>674ms</t>
+          <t>255ms</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -19098,7 +19074,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>618ms</t>
+          <t>636ms</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -19163,7 +19139,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>794ms</t>
+          <t>168ms</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -19228,7 +19204,7 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>658ms</t>
+          <t>461ms</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -19292,7 +19268,7 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>832ms</t>
+          <t>404ms</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -19357,7 +19333,7 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>148ms</t>
+          <t>207ms</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -19422,7 +19398,7 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>413ms</t>
+          <t>510ms</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -19487,7 +19463,7 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>251ms</t>
+          <t>185ms</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
@@ -19552,7 +19528,7 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>292ms</t>
+          <t>512ms</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -19617,7 +19593,7 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>441ms</t>
+          <t>167ms</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
@@ -19681,7 +19657,7 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>809ms</t>
+          <t>465ms</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -19746,7 +19722,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>594ms</t>
+          <t>323ms</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
@@ -19811,7 +19787,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>390ms</t>
+          <t>544ms</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
@@ -19876,7 +19852,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>446ms</t>
+          <t>841ms</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -19942,7 +19918,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>537ms</t>
+          <t>174ms</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">

--- a/reports/selenium-web-report.xlsx
+++ b/reports/selenium-web-report.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>816ms</t>
+          <t>367ms</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>602ms</t>
+          <t>468ms</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>664ms</t>
+          <t>503ms</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>781ms</t>
+          <t>669ms</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>380ms</t>
+          <t>411ms</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>677ms</t>
+          <t>632ms</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>625ms</t>
+          <t>835ms</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>455ms</t>
+          <t>296ms</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>503ms</t>
+          <t>749ms</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>304ms</t>
+          <t>132ms</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>604ms</t>
+          <t>137ms</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>142ms</t>
+          <t>704ms</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>355ms</t>
+          <t>571ms</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>146ms</t>
+          <t>529ms</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>674ms</t>
+          <t>448ms</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>721ms</t>
+          <t>212ms</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>272ms</t>
+          <t>559ms</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>339ms</t>
+          <t>742ms</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>575ms</t>
+          <t>835ms</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>264ms</t>
+          <t>789ms</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>804ms</t>
+          <t>842ms</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>811ms</t>
+          <t>835ms</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>250ms</t>
+          <t>421ms</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>789ms</t>
+          <t>806ms</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>796ms</t>
+          <t>139ms</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>209ms</t>
+          <t>537ms</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>381ms</t>
+          <t>774ms</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>685ms</t>
+          <t>200ms</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>676ms</t>
+          <t>236ms</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>344ms</t>
+          <t>361ms</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>810ms</t>
+          <t>204ms</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>456ms</t>
+          <t>238ms</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>158ms</t>
+          <t>540ms</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>137ms</t>
+          <t>151ms</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>743ms</t>
+          <t>198ms</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>762ms</t>
+          <t>349ms</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>394ms</t>
+          <t>234ms</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>135ms</t>
+          <t>619ms</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>534ms</t>
+          <t>377ms</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>447ms</t>
+          <t>146ms</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>449ms</t>
+          <t>343ms</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>774ms</t>
+          <t>546ms</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>285ms</t>
+          <t>467ms</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>460ms</t>
+          <t>498ms</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>222ms</t>
+          <t>465ms</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>551ms</t>
+          <t>435ms</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>439ms</t>
+          <t>690ms</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>813ms</t>
+          <t>741ms</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>649ms</t>
+          <t>704ms</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>308ms</t>
+          <t>429ms</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>679ms</t>
+          <t>781ms</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>407ms</t>
+          <t>294ms</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>419ms</t>
+          <t>357ms</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>299ms</t>
+          <t>601ms</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>364ms</t>
+          <t>386ms</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>371ms</t>
+          <t>577ms</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>281ms</t>
+          <t>501ms</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>277ms</t>
+          <t>525ms</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>681ms</t>
+          <t>736ms</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>183ms</t>
+          <t>135ms</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>526ms</t>
+          <t>208ms</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>652ms</t>
+          <t>199ms</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>318ms</t>
+          <t>189ms</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>661ms</t>
+          <t>793ms</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>202ms</t>
+          <t>194ms</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>171ms</t>
+          <t>691ms</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>274ms</t>
+          <t>455ms</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>415ms</t>
+          <t>715ms</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>126ms</t>
+          <t>663ms</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>323ms</t>
+          <t>140ms</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>325ms</t>
+          <t>705ms</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>676ms</t>
+          <t>595ms</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>477ms</t>
+          <t>367ms</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>376ms</t>
+          <t>143ms</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>612ms</t>
+          <t>452ms</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>443ms</t>
+          <t>818ms</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>199ms</t>
+          <t>197ms</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>478ms</t>
+          <t>710ms</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>741ms</t>
+          <t>178ms</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>271ms</t>
+          <t>704ms</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>825ms</t>
+          <t>672ms</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>829ms</t>
+          <t>273ms</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>838ms</t>
+          <t>184ms</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>837ms</t>
+          <t>392ms</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>794ms</t>
+          <t>414ms</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>480ms</t>
+          <t>768ms</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>141ms</t>
+          <t>502ms</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>519ms</t>
+          <t>480ms</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>803ms</t>
+          <t>380ms</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>402ms</t>
+          <t>146ms</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>382ms</t>
+          <t>485ms</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>137ms</t>
+          <t>761ms</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>133ms</t>
+          <t>195ms</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>299ms</t>
+          <t>147ms</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>136ms</t>
+          <t>506ms</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>533ms</t>
+          <t>759ms</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>454ms</t>
+          <t>169ms</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>601ms</t>
+          <t>607ms</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>509ms</t>
+          <t>466ms</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>791ms</t>
+          <t>639ms</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>647ms</t>
+          <t>289ms</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>425ms</t>
+          <t>665ms</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>413ms</t>
+          <t>488ms</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>736ms</t>
+          <t>616ms</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>756ms</t>
+          <t>121ms</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>608ms</t>
+          <t>201ms</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>148ms</t>
+          <t>430ms</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>414ms</t>
+          <t>824ms</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>471ms</t>
+          <t>258ms</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>271ms</t>
+          <t>287ms</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>247ms</t>
+          <t>171ms</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>694ms</t>
+          <t>292ms</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>440ms</t>
+          <t>472ms</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>244ms</t>
+          <t>785ms</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>334ms</t>
+          <t>415ms</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>673ms</t>
+          <t>358ms</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>149ms</t>
+          <t>548ms</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>195ms</t>
+          <t>306ms</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>510ms</t>
+          <t>507ms</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>446ms</t>
+          <t>822ms</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>394ms</t>
+          <t>716ms</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>632ms</t>
+          <t>535ms</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>720ms</t>
+          <t>227ms</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>266ms</t>
+          <t>834ms</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>759ms</t>
+          <t>173ms</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>120ms</t>
+          <t>371ms</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>675ms</t>
+          <t>360ms</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>539ms</t>
+          <t>751ms</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>742ms</t>
+          <t>451ms</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>394ms</t>
+          <t>541ms</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>255ms</t>
+          <t>200ms</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>570ms</t>
+          <t>277ms</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>345ms</t>
+          <t>360ms</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>261ms</t>
+          <t>675ms</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>241ms</t>
+          <t>224ms</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>551ms</t>
+          <t>314ms</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>129ms</t>
+          <t>148ms</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>370ms</t>
+          <t>720ms</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>291ms</t>
+          <t>826ms</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>281ms</t>
+          <t>121ms</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>539ms</t>
+          <t>709ms</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>142ms</t>
+          <t>212ms</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>601ms</t>
+          <t>774ms</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>583ms</t>
+          <t>476ms</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>181ms</t>
+          <t>494ms</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>612ms</t>
+          <t>627ms</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>773ms</t>
+          <t>845ms</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>446ms</t>
+          <t>598ms</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>651ms</t>
+          <t>154ms</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>603ms</t>
+          <t>794ms</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>321ms</t>
+          <t>137ms</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>224ms</t>
+          <t>779ms</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>601ms</t>
+          <t>604ms</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>183ms</t>
+          <t>189ms</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>417ms</t>
+          <t>735ms</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>316ms</t>
+          <t>187ms</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>486ms</t>
+          <t>222ms</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>364ms</t>
+          <t>455ms</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>839ms</t>
+          <t>437ms</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>761ms</t>
+          <t>795ms</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>170ms</t>
+          <t>220ms</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>247ms</t>
+          <t>152ms</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>639ms</t>
+          <t>492ms</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>148ms</t>
+          <t>634ms</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>529ms</t>
+          <t>222ms</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>573ms</t>
+          <t>593ms</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>485ms</t>
+          <t>500ms</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>191ms</t>
+          <t>298ms</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>469ms</t>
+          <t>528ms</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -11567,7 +11567,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>351ms</t>
+          <t>357ms</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>453ms</t>
+          <t>485ms</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>155ms</t>
+          <t>730ms</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>477ms</t>
+          <t>784ms</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>634ms</t>
+          <t>672ms</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>823ms</t>
+          <t>549ms</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>304ms</t>
+          <t>758ms</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>193ms</t>
+          <t>739ms</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -12085,7 +12085,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>751ms</t>
+          <t>174ms</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -12150,7 +12150,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>749ms</t>
+          <t>598ms</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>242ms</t>
+          <t>688ms</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>428ms</t>
+          <t>215ms</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>621ms</t>
+          <t>623ms</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>376ms</t>
+          <t>605ms</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>714ms</t>
+          <t>770ms</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>671ms</t>
+          <t>632ms</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -12607,7 +12607,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>440ms</t>
+          <t>258ms</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -12672,7 +12672,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>630ms</t>
+          <t>730ms</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>225ms</t>
+          <t>543ms</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>281ms</t>
+          <t>400ms</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>488ms</t>
+          <t>177ms</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>434ms</t>
+          <t>482ms</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>379ms</t>
+          <t>590ms</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>296ms</t>
+          <t>604ms</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>495ms</t>
+          <t>638ms</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>457ms</t>
+          <t>523ms</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>477ms</t>
+          <t>187ms</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>326ms</t>
+          <t>666ms</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>456ms</t>
+          <t>121ms</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>822ms</t>
+          <t>617ms</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>512ms</t>
+          <t>849ms</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>527ms</t>
+          <t>351ms</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -13637,7 +13637,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>223ms</t>
+          <t>665ms</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -13702,7 +13702,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>159ms</t>
+          <t>796ms</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>280ms</t>
+          <t>703ms</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>774ms</t>
+          <t>808ms</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -13896,7 +13896,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>209ms</t>
+          <t>168ms</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -13961,7 +13961,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>718ms</t>
+          <t>346ms</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>223ms</t>
+          <t>555ms</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>480ms</t>
+          <t>211ms</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>554ms</t>
+          <t>663ms</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -14220,7 +14220,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>479ms</t>
+          <t>244ms</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>312ms</t>
+          <t>341ms</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -14350,7 +14350,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>468ms</t>
+          <t>302ms</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -14415,7 +14415,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>161ms</t>
+          <t>706ms</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>164ms</t>
+          <t>730ms</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -14545,7 +14545,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>218ms</t>
+          <t>146ms</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -14609,7 +14609,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>792ms</t>
+          <t>726ms</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -14674,7 +14674,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>580ms</t>
+          <t>646ms</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>646ms</t>
+          <t>822ms</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>444ms</t>
+          <t>277ms</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -14870,7 +14870,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>650ms</t>
+          <t>225ms</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -14936,7 +14936,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>584ms</t>
+          <t>180ms</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>448ms</t>
+          <t>195ms</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -15066,7 +15066,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>769ms</t>
+          <t>361ms</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -15131,7 +15131,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>731ms</t>
+          <t>783ms</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>515ms</t>
+          <t>579ms</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>444ms</t>
+          <t>715ms</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -15325,7 +15325,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>698ms</t>
+          <t>382ms</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -15388,7 +15388,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>382ms</t>
+          <t>241ms</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -15451,7 +15451,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>286ms</t>
+          <t>260ms</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>839ms</t>
+          <t>421ms</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -15578,7 +15578,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>547ms</t>
+          <t>837ms</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>568ms</t>
+          <t>354ms</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -15707,7 +15707,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>733ms</t>
+          <t>772ms</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>627ms</t>
+          <t>430ms</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -15837,7 +15837,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>137ms</t>
+          <t>356ms</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -15902,7 +15902,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>600ms</t>
+          <t>145ms</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>435ms</t>
+          <t>573ms</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -16032,7 +16032,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>366ms</t>
+          <t>714ms</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -16096,7 +16096,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>559ms</t>
+          <t>137ms</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -16161,7 +16161,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>154ms</t>
+          <t>628ms</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>725ms</t>
+          <t>144ms</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>402ms</t>
+          <t>834ms</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>230ms</t>
+          <t>149ms</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -16420,7 +16420,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>632ms</t>
+          <t>244ms</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -16485,7 +16485,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>493ms</t>
+          <t>195ms</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -16550,7 +16550,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>741ms</t>
+          <t>273ms</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -16615,7 +16615,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>327ms</t>
+          <t>251ms</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>478ms</t>
+          <t>274ms</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>292ms</t>
+          <t>502ms</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -16809,7 +16809,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>304ms</t>
+          <t>833ms</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>586ms</t>
+          <t>354ms</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -16939,7 +16939,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>813ms</t>
+          <t>471ms</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -17004,7 +17004,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>399ms</t>
+          <t>694ms</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -17069,7 +17069,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>596ms</t>
+          <t>561ms</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -17133,7 +17133,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>600ms</t>
+          <t>349ms</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -17198,7 +17198,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>767ms</t>
+          <t>481ms</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>596ms</t>
+          <t>562ms</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>766ms</t>
+          <t>825ms</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -17394,7 +17394,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>568ms</t>
+          <t>481ms</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -17460,7 +17460,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>195ms</t>
+          <t>302ms</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -17525,7 +17525,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>707ms</t>
+          <t>808ms</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -17590,7 +17590,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>190ms</t>
+          <t>461ms</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -17655,7 +17655,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>667ms</t>
+          <t>833ms</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -17720,7 +17720,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>634ms</t>
+          <t>710ms</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -17784,7 +17784,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>428ms</t>
+          <t>187ms</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -17849,7 +17849,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>768ms</t>
+          <t>492ms</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -17912,7 +17912,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>688ms</t>
+          <t>142ms</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -17975,7 +17975,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>484ms</t>
+          <t>525ms</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -18038,7 +18038,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>599ms</t>
+          <t>478ms</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -18102,7 +18102,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>317ms</t>
+          <t>242ms</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -18166,7 +18166,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>144ms</t>
+          <t>849ms</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -18231,7 +18231,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>683ms</t>
+          <t>694ms</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>330ms</t>
+          <t>616ms</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>656ms</t>
+          <t>659ms</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>644ms</t>
+          <t>228ms</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>567ms</t>
+          <t>413ms</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -18556,7 +18556,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>398ms</t>
+          <t>373ms</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -18620,7 +18620,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>566ms</t>
+          <t>625ms</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>201ms</t>
+          <t>380ms</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -18750,7 +18750,7 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>803ms</t>
+          <t>367ms</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -18815,7 +18815,7 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>420ms</t>
+          <t>424ms</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -18880,7 +18880,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>623ms</t>
+          <t>332ms</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -18944,7 +18944,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>613ms</t>
+          <t>299ms</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -19009,7 +19009,7 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>255ms</t>
+          <t>436ms</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>636ms</t>
+          <t>459ms</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -19139,7 +19139,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>168ms</t>
+          <t>262ms</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -19204,7 +19204,7 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>461ms</t>
+          <t>688ms</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -19268,7 +19268,7 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>404ms</t>
+          <t>436ms</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -19333,7 +19333,7 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>207ms</t>
+          <t>306ms</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>510ms</t>
+          <t>282ms</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>185ms</t>
+          <t>385ms</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>512ms</t>
+          <t>632ms</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -19593,7 +19593,7 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>167ms</t>
+          <t>564ms</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
@@ -19657,7 +19657,7 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>465ms</t>
+          <t>264ms</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -19722,7 +19722,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>323ms</t>
+          <t>632ms</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
@@ -19787,7 +19787,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>544ms</t>
+          <t>402ms</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
@@ -19852,7 +19852,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>841ms</t>
+          <t>825ms</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -19918,7 +19918,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>174ms</t>
+          <t>543ms</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
